--- a/ssp_modeling/scenario_mapping/NDC_Libya_InventarioMatch.xlsx
+++ b/ssp_modeling/scenario_mapping/NDC_Libya_InventarioMatch.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fabianfuentes/Documents/Claude/Projects/SISEPUEDE/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fabianfuentes/git/ssp_libya/ssp_modeling/scenario_mapping/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D6C528A-99E3-9642-8FBF-2FD892B5E915}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B521157B-E7BB-A645-AB37-B818296A23B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-49880" yWindow="-5900" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inventory × NDC" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="75">
   <si>
     <t>Libya NDC — Historical GHG Inventory 2017-2023 × NDC Mitigation Targets 2026-2035</t>
   </si>
@@ -278,6 +278,11 @@
   </si>
   <si>
     <t>→ STABLE</t>
+  </si>
+  <si>
+    <t>SSP Capex
+TOTAL
+(B USD)</t>
   </si>
 </sst>
 </file>
@@ -645,7 +650,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -707,11 +712,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -986,6 +1011,10 @@
     <xf numFmtId="165" fontId="15" fillId="30" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -994,17 +1023,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="30" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="30" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="30" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1326,56 +1354,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="100" t="s">
+      <c r="A1" s="92" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
-      <c r="D1" s="96"/>
-      <c r="E1" s="96"/>
-      <c r="F1" s="96"/>
-      <c r="G1" s="96"/>
-      <c r="H1" s="96"/>
-      <c r="I1" s="96"/>
-      <c r="J1" s="96"/>
-      <c r="K1" s="96"/>
-      <c r="L1" s="96"/>
-      <c r="M1" s="96"/>
-      <c r="N1" s="96"/>
-      <c r="O1" s="96"/>
-      <c r="P1" s="96"/>
-      <c r="Q1" s="96"/>
-      <c r="R1" s="96"/>
+      <c r="B1" s="93"/>
+      <c r="C1" s="93"/>
+      <c r="D1" s="93"/>
+      <c r="E1" s="93"/>
+      <c r="F1" s="93"/>
+      <c r="G1" s="93"/>
+      <c r="H1" s="93"/>
+      <c r="I1" s="93"/>
+      <c r="J1" s="93"/>
+      <c r="K1" s="93"/>
+      <c r="L1" s="93"/>
+      <c r="M1" s="93"/>
+      <c r="N1" s="93"/>
+      <c r="O1" s="93"/>
+      <c r="P1" s="93"/>
+      <c r="Q1" s="93"/>
+      <c r="R1" s="93"/>
     </row>
     <row r="2" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="92" t="s">
+      <c r="A2" s="94" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="93"/>
-      <c r="C2" s="93"/>
-      <c r="D2" s="93"/>
-      <c r="E2" s="94"/>
-      <c r="F2" s="97" t="s">
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
+      <c r="D2" s="95"/>
+      <c r="E2" s="96"/>
+      <c r="F2" s="98" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="93"/>
-      <c r="H2" s="93"/>
-      <c r="I2" s="93"/>
-      <c r="J2" s="93"/>
-      <c r="K2" s="93"/>
-      <c r="L2" s="94"/>
-      <c r="M2" s="98" t="s">
+      <c r="G2" s="95"/>
+      <c r="H2" s="95"/>
+      <c r="I2" s="95"/>
+      <c r="J2" s="95"/>
+      <c r="K2" s="95"/>
+      <c r="L2" s="96"/>
+      <c r="M2" s="99" t="s">
         <v>3</v>
       </c>
       <c r="N2" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="O2" s="99" t="s">
+      <c r="O2" s="100" t="s">
         <v>5</v>
       </c>
-      <c r="P2" s="96"/>
-      <c r="Q2" s="96"/>
-      <c r="R2" s="96"/>
+      <c r="P2" s="101"/>
+      <c r="Q2" s="101"/>
+      <c r="R2" s="101"/>
     </row>
     <row r="3" spans="1:18" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
@@ -1426,11 +1454,11 @@
       <c r="P3" s="75" t="s">
         <v>21</v>
       </c>
-      <c r="Q3" s="58" t="s">
-        <v>19</v>
-      </c>
-      <c r="R3" s="75" t="s">
+      <c r="Q3" s="75" t="s">
         <v>22</v>
+      </c>
+      <c r="R3" s="58" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -1482,12 +1510,10 @@
       <c r="P4" s="76">
         <v>0.99299999999999999</v>
       </c>
-      <c r="Q4" s="71">
-        <v>83.61</v>
-      </c>
-      <c r="R4" s="77">
+      <c r="Q4" s="77">
         <v>1.2330000000000001</v>
       </c>
+      <c r="R4" s="71"/>
     </row>
     <row r="5" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="9">
@@ -1538,12 +1564,10 @@
       <c r="P5" s="78">
         <v>0.36699999999999999</v>
       </c>
-      <c r="Q5" s="71">
-        <v>33.667000000000002</v>
-      </c>
-      <c r="R5" s="79">
+      <c r="Q5" s="79">
         <v>0.48899999999999999</v>
       </c>
+      <c r="R5" s="71"/>
     </row>
     <row r="6" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="13">
@@ -1592,10 +1616,10 @@
       <c r="P6" s="80">
         <v>0.52800000000000002</v>
       </c>
-      <c r="Q6" s="71"/>
-      <c r="R6" s="77">
+      <c r="Q6" s="77">
         <v>1.6060000000000001</v>
       </c>
+      <c r="R6" s="71"/>
     </row>
     <row r="7" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="13">
@@ -1644,10 +1668,10 @@
       <c r="P7" s="80">
         <v>0.46</v>
       </c>
-      <c r="Q7" s="71"/>
-      <c r="R7" s="79">
+      <c r="Q7" s="79">
         <v>0.61299999999999999</v>
       </c>
+      <c r="R7" s="71"/>
     </row>
     <row r="8" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="18">
@@ -1696,10 +1720,10 @@
       <c r="P8" s="81">
         <v>5.6040000000000001</v>
       </c>
-      <c r="Q8" s="71"/>
-      <c r="R8" s="82">
+      <c r="Q8" s="82">
         <v>7.4720000000000004</v>
       </c>
+      <c r="R8" s="71"/>
     </row>
     <row r="9" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="18">
@@ -1748,10 +1772,10 @@
       <c r="P9" s="81">
         <v>9.7149999999999999</v>
       </c>
-      <c r="Q9" s="71"/>
-      <c r="R9" s="83">
+      <c r="Q9" s="83">
         <v>12.954000000000001</v>
       </c>
+      <c r="R9" s="71"/>
     </row>
     <row r="10" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="21">
@@ -1800,10 +1824,10 @@
       <c r="P10" s="84">
         <v>0</v>
       </c>
-      <c r="Q10" s="71"/>
-      <c r="R10" s="85">
+      <c r="Q10" s="85">
         <v>0</v>
       </c>
+      <c r="R10" s="71"/>
     </row>
     <row r="11" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="13">
@@ -1852,10 +1876,10 @@
       <c r="P11" s="80">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="Q11" s="71"/>
-      <c r="R11" s="79">
+      <c r="Q11" s="79">
         <v>0.109</v>
       </c>
+      <c r="R11" s="71"/>
     </row>
     <row r="12" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="25">
@@ -1904,10 +1928,10 @@
       <c r="P12" s="86">
         <v>0.161</v>
       </c>
-      <c r="Q12" s="71"/>
-      <c r="R12" s="79">
+      <c r="Q12" s="79">
         <v>0.224</v>
       </c>
+      <c r="R12" s="71"/>
     </row>
     <row r="13" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="28">
@@ -1956,10 +1980,10 @@
       <c r="P13" s="87">
         <v>0.373</v>
       </c>
-      <c r="Q13" s="71"/>
-      <c r="R13" s="79">
+      <c r="Q13" s="79">
         <v>0.373</v>
       </c>
+      <c r="R13" s="71"/>
     </row>
     <row r="14" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="31">
@@ -1998,7 +2022,7 @@
       <c r="L14" s="65">
         <v>0.76200000000000001</v>
       </c>
-      <c r="M14" s="74">
+      <c r="M14" s="71">
         <v>1.5429999999999999</v>
       </c>
       <c r="N14" s="71">
@@ -2010,12 +2034,10 @@
       <c r="P14" s="88">
         <v>0.108</v>
       </c>
-      <c r="Q14" s="71">
-        <v>1.78</v>
-      </c>
-      <c r="R14" s="79">
+      <c r="Q14" s="79">
         <v>0.17899999999999999</v>
       </c>
+      <c r="R14" s="71"/>
     </row>
     <row r="15" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="31">
@@ -2054,7 +2076,7 @@
       <c r="L15" s="65">
         <v>0.496</v>
       </c>
-      <c r="M15" s="74">
+      <c r="M15" s="71">
         <v>0.25800000000000001</v>
       </c>
       <c r="N15" s="71">
@@ -2066,12 +2088,10 @@
       <c r="P15" s="88">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="Q15" s="71">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="R15" s="79">
+      <c r="Q15" s="79">
         <v>0.06</v>
       </c>
+      <c r="R15" s="71"/>
     </row>
     <row r="16" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="35">
@@ -2110,7 +2130,7 @@
       <c r="L16" s="65">
         <v>3.4289999999999998</v>
       </c>
-      <c r="M16" s="71">
+      <c r="M16" s="74">
         <v>3.919</v>
       </c>
       <c r="N16" s="71"/>
@@ -2120,10 +2140,10 @@
       <c r="P16" s="89">
         <v>3.6999999999999998E-2</v>
       </c>
-      <c r="Q16" s="71"/>
-      <c r="R16" s="79">
+      <c r="Q16" s="79">
         <v>4.9000000000000002E-2</v>
       </c>
+      <c r="R16" s="71"/>
     </row>
     <row r="17" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="38">
@@ -2174,12 +2194,10 @@
       <c r="P17" s="90">
         <v>3.2829999999999999</v>
       </c>
-      <c r="Q17" s="71">
-        <v>12.85</v>
-      </c>
-      <c r="R17" s="82">
+      <c r="Q17" s="82">
         <v>5.6989999999999998</v>
       </c>
+      <c r="R17" s="71"/>
     </row>
     <row r="18" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="41" t="s">
@@ -2226,31 +2244,31 @@
       <c r="P18" s="91">
         <v>21.672000000000001</v>
       </c>
-      <c r="Q18" s="73">
-        <f>+SUM(Q4:Q17)</f>
-        <v>132.477</v>
-      </c>
-      <c r="R18" s="91">
+      <c r="Q18" s="91">
         <v>31.06</v>
       </c>
+      <c r="R18" s="73">
+        <f>+SUM(R4:R17)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="20" spans="1:18" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="95" t="s">
+      <c r="A20" s="97" t="s">
         <v>65</v>
       </c>
-      <c r="B20" s="96"/>
-      <c r="C20" s="96"/>
-      <c r="D20" s="96"/>
-      <c r="E20" s="96"/>
-      <c r="F20" s="96"/>
-      <c r="G20" s="96"/>
-      <c r="H20" s="96"/>
-      <c r="I20" s="96"/>
-      <c r="J20" s="96"/>
-      <c r="K20" s="96"/>
-      <c r="L20" s="96"/>
-      <c r="M20" s="96"/>
-      <c r="N20" s="96"/>
+      <c r="B20" s="93"/>
+      <c r="C20" s="93"/>
+      <c r="D20" s="93"/>
+      <c r="E20" s="93"/>
+      <c r="F20" s="93"/>
+      <c r="G20" s="93"/>
+      <c r="H20" s="93"/>
+      <c r="I20" s="93"/>
+      <c r="J20" s="93"/>
+      <c r="K20" s="93"/>
+      <c r="L20" s="93"/>
+      <c r="M20" s="93"/>
+      <c r="N20" s="93"/>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/ssp_modeling/scenario_mapping/NDC_Libya_InventarioMatch.xlsx
+++ b/ssp_modeling/scenario_mapping/NDC_Libya_InventarioMatch.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fabianfuentes/git/ssp_libya/ssp_modeling/scenario_mapping/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B521157B-E7BB-A645-AB37-B818296A23B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24426D7D-815A-BD4F-9FA3-1AB87907A868}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-47440" yWindow="-7160" windowWidth="44860" windowHeight="28080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inventory × NDC" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="76">
   <si>
     <t>Libya NDC — Historical GHG Inventory 2017-2023 × NDC Mitigation Targets 2026-2035</t>
   </si>
@@ -283,6 +283,9 @@
     <t>SSP Capex
 TOTAL
 (B USD)</t>
+  </si>
+  <si>
+    <t>Error</t>
   </si>
 </sst>
 </file>
@@ -293,7 +296,7 @@
     <numFmt numFmtId="164" formatCode="\+0.0%;\-0.0%;0.0%"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -437,6 +440,13 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="36">
     <fill>
@@ -733,10 +743,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1035,9 +1046,22 @@
     <xf numFmtId="0" fontId="15" fillId="30" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="29" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="15" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1337,7 +1361,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R20"/>
+  <dimension ref="A1:S20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -1347,13 +1371,13 @@
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="12" width="10" customWidth="1"/>
     <col min="13" max="13" width="16" customWidth="1"/>
-    <col min="14" max="14" width="16.6640625" customWidth="1"/>
-    <col min="15" max="16" width="13" customWidth="1"/>
-    <col min="17" max="17" width="16.6640625" customWidth="1"/>
-    <col min="18" max="18" width="13" customWidth="1"/>
+    <col min="14" max="15" width="16.6640625" customWidth="1"/>
+    <col min="16" max="17" width="13" customWidth="1"/>
+    <col min="18" max="18" width="16.6640625" customWidth="1"/>
+    <col min="19" max="19" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:19" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="92" t="s">
         <v>0</v>
       </c>
@@ -1374,8 +1398,9 @@
       <c r="P1" s="93"/>
       <c r="Q1" s="93"/>
       <c r="R1" s="93"/>
-    </row>
-    <row r="2" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="S1" s="93"/>
+    </row>
+    <row r="2" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="94" t="s">
         <v>1</v>
       </c>
@@ -1398,14 +1423,15 @@
       <c r="N2" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="O2" s="100" t="s">
+      <c r="O2" s="102"/>
+      <c r="P2" s="100" t="s">
         <v>5</v>
       </c>
-      <c r="P2" s="101"/>
       <c r="Q2" s="101"/>
       <c r="R2" s="101"/>
-    </row>
-    <row r="3" spans="1:18" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="S2" s="101"/>
+    </row>
+    <row r="3" spans="1:19" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -1448,20 +1474,23 @@
       <c r="N3" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="O3" s="75" t="s">
+      <c r="O3" s="103" t="s">
+        <v>75</v>
+      </c>
+      <c r="P3" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="P3" s="75" t="s">
+      <c r="Q3" s="75" t="s">
         <v>21</v>
       </c>
-      <c r="Q3" s="75" t="s">
+      <c r="R3" s="75" t="s">
         <v>22</v>
       </c>
-      <c r="R3" s="58" t="s">
+      <c r="S3" s="58" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:19" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4">
         <v>1</v>
       </c>
@@ -1504,18 +1533,22 @@
       <c r="N4" s="71">
         <v>83.61</v>
       </c>
-      <c r="O4" s="76">
+      <c r="O4" s="105">
+        <f>+(N4/M4)-1</f>
+        <v>-1.6283502364872859E-2</v>
+      </c>
+      <c r="P4" s="76">
         <v>0.24099999999999999</v>
       </c>
-      <c r="P4" s="76">
+      <c r="Q4" s="76">
         <v>0.99299999999999999</v>
       </c>
-      <c r="Q4" s="77">
+      <c r="R4" s="77">
         <v>1.2330000000000001</v>
       </c>
-      <c r="R4" s="71"/>
-    </row>
-    <row r="5" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="S4" s="71"/>
+    </row>
+    <row r="5" spans="1:19" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="9">
         <v>2</v>
       </c>
@@ -1558,18 +1591,22 @@
       <c r="N5" s="71">
         <v>33.667000000000002</v>
       </c>
-      <c r="O5" s="78">
+      <c r="O5" s="105">
+        <f t="shared" ref="O5:O17" si="0">+(N5/M5)-1</f>
+        <v>-0.14092880836948196</v>
+      </c>
+      <c r="P5" s="78">
         <v>0.122</v>
       </c>
-      <c r="P5" s="78">
+      <c r="Q5" s="78">
         <v>0.36699999999999999</v>
       </c>
-      <c r="Q5" s="79">
+      <c r="R5" s="79">
         <v>0.48899999999999999</v>
       </c>
-      <c r="R5" s="71"/>
-    </row>
-    <row r="6" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="S5" s="71"/>
+    </row>
+    <row r="6" spans="1:19" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="13">
         <v>3</v>
       </c>
@@ -1610,18 +1647,19 @@
         <v>24.951000000000001</v>
       </c>
       <c r="N6" s="71"/>
-      <c r="O6" s="80">
+      <c r="O6" s="105"/>
+      <c r="P6" s="80">
         <v>1.0780000000000001</v>
       </c>
-      <c r="P6" s="80">
+      <c r="Q6" s="80">
         <v>0.52800000000000002</v>
       </c>
-      <c r="Q6" s="77">
+      <c r="R6" s="77">
         <v>1.6060000000000001</v>
       </c>
-      <c r="R6" s="71"/>
-    </row>
-    <row r="7" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="S6" s="71"/>
+    </row>
+    <row r="7" spans="1:19" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="13">
         <v>4</v>
       </c>
@@ -1662,18 +1700,19 @@
         <v>9.5299999999999994</v>
       </c>
       <c r="N7" s="71"/>
-      <c r="O7" s="80">
+      <c r="O7" s="105"/>
+      <c r="P7" s="80">
         <v>0.153</v>
       </c>
-      <c r="P7" s="80">
+      <c r="Q7" s="80">
         <v>0.46</v>
       </c>
-      <c r="Q7" s="79">
+      <c r="R7" s="79">
         <v>0.61299999999999999</v>
       </c>
-      <c r="R7" s="71"/>
-    </row>
-    <row r="8" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="S7" s="71"/>
+    </row>
+    <row r="8" spans="1:19" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="18">
         <v>5</v>
       </c>
@@ -1714,18 +1753,19 @@
         <v>69.394999999999996</v>
       </c>
       <c r="N8" s="71"/>
-      <c r="O8" s="81">
+      <c r="O8" s="105"/>
+      <c r="P8" s="81">
         <v>1.8680000000000001</v>
       </c>
-      <c r="P8" s="81">
+      <c r="Q8" s="81">
         <v>5.6040000000000001</v>
       </c>
-      <c r="Q8" s="82">
+      <c r="R8" s="82">
         <v>7.4720000000000004</v>
       </c>
-      <c r="R8" s="71"/>
-    </row>
-    <row r="9" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="S8" s="71"/>
+    </row>
+    <row r="9" spans="1:19" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="18">
         <v>6</v>
       </c>
@@ -1766,18 +1806,19 @@
         <v>24.693000000000001</v>
       </c>
       <c r="N9" s="71"/>
-      <c r="O9" s="81">
+      <c r="O9" s="105"/>
+      <c r="P9" s="81">
         <v>3.238</v>
       </c>
-      <c r="P9" s="81">
+      <c r="Q9" s="81">
         <v>9.7149999999999999</v>
       </c>
-      <c r="Q9" s="83">
+      <c r="R9" s="83">
         <v>12.954000000000001</v>
       </c>
-      <c r="R9" s="71"/>
-    </row>
-    <row r="10" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="S9" s="71"/>
+    </row>
+    <row r="10" spans="1:19" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="21">
         <v>7</v>
       </c>
@@ -1818,18 +1859,19 @@
         <v>1.135</v>
       </c>
       <c r="N10" s="71"/>
-      <c r="O10" s="84">
-        <v>0</v>
-      </c>
+      <c r="O10" s="105"/>
       <c r="P10" s="84">
         <v>0</v>
       </c>
-      <c r="Q10" s="85">
+      <c r="Q10" s="84">
         <v>0</v>
       </c>
-      <c r="R10" s="71"/>
-    </row>
-    <row r="11" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R10" s="85">
+        <v>0</v>
+      </c>
+      <c r="S10" s="71"/>
+    </row>
+    <row r="11" spans="1:19" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="13">
         <v>8</v>
       </c>
@@ -1870,18 +1912,19 @@
         <v>1.69</v>
       </c>
       <c r="N11" s="71"/>
-      <c r="O11" s="80">
+      <c r="O11" s="105"/>
+      <c r="P11" s="80">
         <v>0.10100000000000001</v>
       </c>
-      <c r="P11" s="80">
+      <c r="Q11" s="80">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="Q11" s="79">
+      <c r="R11" s="79">
         <v>0.109</v>
       </c>
-      <c r="R11" s="71"/>
-    </row>
-    <row r="12" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="S11" s="71"/>
+    </row>
+    <row r="12" spans="1:19" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="25">
         <v>9</v>
       </c>
@@ -1922,18 +1965,19 @@
         <v>1.482</v>
       </c>
       <c r="N12" s="71"/>
-      <c r="O12" s="86">
+      <c r="O12" s="105"/>
+      <c r="P12" s="86">
         <v>6.2E-2</v>
       </c>
-      <c r="P12" s="86">
+      <c r="Q12" s="86">
         <v>0.161</v>
       </c>
-      <c r="Q12" s="79">
+      <c r="R12" s="79">
         <v>0.224</v>
       </c>
-      <c r="R12" s="71"/>
-    </row>
-    <row r="13" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="S12" s="71"/>
+    </row>
+    <row r="13" spans="1:19" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="28">
         <v>10</v>
       </c>
@@ -1974,18 +2018,19 @@
         <v>1.863</v>
       </c>
       <c r="N13" s="71"/>
-      <c r="O13" s="84">
+      <c r="O13" s="105"/>
+      <c r="P13" s="84">
         <v>0</v>
       </c>
-      <c r="P13" s="87">
+      <c r="Q13" s="87">
         <v>0.373</v>
       </c>
-      <c r="Q13" s="79">
+      <c r="R13" s="79">
         <v>0.373</v>
       </c>
-      <c r="R13" s="71"/>
-    </row>
-    <row r="14" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="S13" s="71"/>
+    </row>
+    <row r="14" spans="1:19" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="31">
         <v>11</v>
       </c>
@@ -2026,20 +2071,24 @@
         <v>1.5429999999999999</v>
       </c>
       <c r="N14" s="71">
-        <v>1.5509999999999999</v>
-      </c>
-      <c r="O14" s="88">
+        <v>1.65</v>
+      </c>
+      <c r="O14" s="105">
+        <f t="shared" si="0"/>
+        <v>6.934543097861301E-2</v>
+      </c>
+      <c r="P14" s="88">
         <v>7.0999999999999994E-2</v>
       </c>
-      <c r="P14" s="88">
+      <c r="Q14" s="88">
         <v>0.108</v>
       </c>
-      <c r="Q14" s="79">
+      <c r="R14" s="79">
         <v>0.17899999999999999</v>
       </c>
-      <c r="R14" s="71"/>
-    </row>
-    <row r="15" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="S14" s="71"/>
+    </row>
+    <row r="15" spans="1:19" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="31">
         <v>12</v>
       </c>
@@ -2080,20 +2129,24 @@
         <v>0.25800000000000001</v>
       </c>
       <c r="N15" s="71">
-        <v>0.30099999999999999</v>
-      </c>
-      <c r="O15" s="88">
+        <v>0.25319999999999998</v>
+      </c>
+      <c r="O15" s="105">
+        <f t="shared" si="0"/>
+        <v>-1.8604651162790753E-2</v>
+      </c>
+      <c r="P15" s="88">
         <v>2.4E-2</v>
       </c>
-      <c r="P15" s="88">
+      <c r="Q15" s="88">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="Q15" s="79">
+      <c r="R15" s="79">
         <v>0.06</v>
       </c>
-      <c r="R15" s="71"/>
-    </row>
-    <row r="16" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="S15" s="71"/>
+    </row>
+    <row r="16" spans="1:19" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="35">
         <v>13</v>
       </c>
@@ -2133,19 +2186,25 @@
       <c r="M16" s="74">
         <v>3.919</v>
       </c>
-      <c r="N16" s="71"/>
-      <c r="O16" s="89">
+      <c r="N16" s="71">
+        <v>4.1029999999999998</v>
+      </c>
+      <c r="O16" s="105">
+        <f t="shared" si="0"/>
+        <v>4.6950752743046609E-2</v>
+      </c>
+      <c r="P16" s="89">
         <v>1.2E-2</v>
       </c>
-      <c r="P16" s="89">
+      <c r="Q16" s="89">
         <v>3.6999999999999998E-2</v>
       </c>
-      <c r="Q16" s="79">
+      <c r="R16" s="79">
         <v>4.9000000000000002E-2</v>
       </c>
-      <c r="R16" s="71"/>
-    </row>
-    <row r="17" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="S16" s="71"/>
+    </row>
+    <row r="17" spans="1:19" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="38">
         <v>14</v>
       </c>
@@ -2188,18 +2247,22 @@
       <c r="N17" s="71">
         <v>12.85</v>
       </c>
-      <c r="O17" s="90">
+      <c r="O17" s="105">
+        <f t="shared" si="0"/>
+        <v>-5.494930732915404E-3</v>
+      </c>
+      <c r="P17" s="90">
         <v>2.4159999999999999</v>
       </c>
-      <c r="P17" s="90">
+      <c r="Q17" s="90">
         <v>3.2829999999999999</v>
       </c>
-      <c r="Q17" s="82">
+      <c r="R17" s="82">
         <v>5.6989999999999998</v>
       </c>
-      <c r="R17" s="71"/>
-    </row>
-    <row r="18" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="S17" s="71"/>
+    </row>
+    <row r="18" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="41" t="s">
         <v>63</v>
       </c>
@@ -2236,23 +2299,24 @@
       </c>
       <c r="N18" s="73">
         <f>+SUM(N4:N17)</f>
-        <v>131.97900000000001</v>
-      </c>
-      <c r="O18" s="91">
+        <v>136.13320000000002</v>
+      </c>
+      <c r="O18" s="104"/>
+      <c r="P18" s="91">
         <v>9.3859999999999992</v>
       </c>
-      <c r="P18" s="91">
+      <c r="Q18" s="91">
         <v>21.672000000000001</v>
       </c>
-      <c r="Q18" s="91">
+      <c r="R18" s="91">
         <v>31.06</v>
       </c>
-      <c r="R18" s="73">
-        <f>+SUM(R4:R17)</f>
+      <c r="S18" s="73">
+        <f>+SUM(S4:S17)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:19" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="97" t="s">
         <v>65</v>
       </c>
@@ -2272,12 +2336,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="A1:S1"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A20:N20"/>
     <mergeCell ref="F2:L2"/>
     <mergeCell ref="M2"/>
-    <mergeCell ref="O2:R2"/>
+    <mergeCell ref="P2:S2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ssp_modeling/scenario_mapping/NDC_Libya_InventarioMatch.xlsx
+++ b/ssp_modeling/scenario_mapping/NDC_Libya_InventarioMatch.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fabianfuentes/git/ssp_libya/ssp_modeling/scenario_mapping/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24426D7D-815A-BD4F-9FA3-1AB87907A868}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26AB1892-BE7D-A147-8302-25595E3D4795}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-47440" yWindow="-7160" windowWidth="44860" windowHeight="28080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-31280" yWindow="-7160" windowWidth="24520" windowHeight="23380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inventory × NDC" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="76">
   <si>
     <t>Libya NDC — Historical GHG Inventory 2017-2023 × NDC Mitigation Targets 2026-2035</t>
   </si>
@@ -74,10 +74,6 @@
 Sector</t>
   </si>
   <si>
-    <t>Modeling
-Priority</t>
-  </si>
-  <si>
     <t>2017</t>
   </si>
   <si>
@@ -286,6 +282,9 @@
   </si>
   <si>
     <t>Error</t>
+  </si>
+  <si>
+    <t>3500/</t>
   </si>
 </sst>
 </file>
@@ -448,7 +447,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -657,6 +656,24 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F3F4"/>
         <bgColor rgb="FFF2F3F4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor rgb="FFFFF3CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor rgb="FFF0E6FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor rgb="FFE8DAEF"/>
       </patternFill>
     </fill>
   </fills>
@@ -747,7 +764,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -815,9 +832,6 @@
     <xf numFmtId="0" fontId="5" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -827,18 +841,12 @@
     <xf numFmtId="0" fontId="5" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -904,18 +912,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1056,6 +1052,33 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="7" fillId="15" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="36" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="36" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="36" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="37" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="38" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1361,77 +1384,74 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S20"/>
+  <dimension ref="A1:R25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
     <col min="3" max="3" width="13" customWidth="1"/>
     <col min="4" max="4" width="22" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="12" width="10" customWidth="1"/>
-    <col min="13" max="13" width="16" customWidth="1"/>
-    <col min="14" max="15" width="16.6640625" customWidth="1"/>
-    <col min="16" max="17" width="13" customWidth="1"/>
-    <col min="18" max="18" width="16.6640625" customWidth="1"/>
-    <col min="19" max="19" width="13" customWidth="1"/>
+    <col min="5" max="11" width="10" customWidth="1"/>
+    <col min="12" max="12" width="16" customWidth="1"/>
+    <col min="13" max="14" width="16.6640625" customWidth="1"/>
+    <col min="15" max="16" width="13" customWidth="1"/>
+    <col min="17" max="17" width="16.6640625" customWidth="1"/>
+    <col min="18" max="18" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="92" t="s">
+    <row r="1" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="85" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="93"/>
-      <c r="C1" s="93"/>
-      <c r="D1" s="93"/>
-      <c r="E1" s="93"/>
-      <c r="F1" s="93"/>
-      <c r="G1" s="93"/>
-      <c r="H1" s="93"/>
-      <c r="I1" s="93"/>
-      <c r="J1" s="93"/>
-      <c r="K1" s="93"/>
-      <c r="L1" s="93"/>
-      <c r="M1" s="93"/>
-      <c r="N1" s="93"/>
-      <c r="O1" s="93"/>
-      <c r="P1" s="93"/>
-      <c r="Q1" s="93"/>
-      <c r="R1" s="93"/>
-      <c r="S1" s="93"/>
-    </row>
-    <row r="2" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="94" t="s">
+      <c r="B1" s="86"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="86"/>
+      <c r="F1" s="86"/>
+      <c r="G1" s="86"/>
+      <c r="H1" s="86"/>
+      <c r="I1" s="86"/>
+      <c r="J1" s="86"/>
+      <c r="K1" s="86"/>
+      <c r="L1" s="86"/>
+      <c r="M1" s="86"/>
+      <c r="N1" s="86"/>
+      <c r="O1" s="86"/>
+      <c r="P1" s="86"/>
+      <c r="Q1" s="86"/>
+      <c r="R1" s="86"/>
+    </row>
+    <row r="2" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="87" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="95"/>
-      <c r="C2" s="95"/>
-      <c r="D2" s="95"/>
-      <c r="E2" s="96"/>
-      <c r="F2" s="98" t="s">
+      <c r="B2" s="88"/>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="91" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="95"/>
-      <c r="H2" s="95"/>
-      <c r="I2" s="95"/>
-      <c r="J2" s="95"/>
-      <c r="K2" s="95"/>
-      <c r="L2" s="96"/>
-      <c r="M2" s="99" t="s">
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="88"/>
+      <c r="K2" s="89"/>
+      <c r="L2" s="92" t="s">
         <v>3</v>
       </c>
-      <c r="N2" s="57" t="s">
+      <c r="M2" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="O2" s="102"/>
-      <c r="P2" s="100" t="s">
+      <c r="N2" s="95"/>
+      <c r="O2" s="93" t="s">
         <v>5</v>
       </c>
-      <c r="Q2" s="101"/>
-      <c r="R2" s="101"/>
-      <c r="S2" s="101"/>
-    </row>
-    <row r="3" spans="1:19" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P2" s="94"/>
+      <c r="Q2" s="94"/>
+      <c r="R2" s="94"/>
+    </row>
+    <row r="3" spans="1:18" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -1444,7 +1464,7 @@
       <c r="D3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F3" s="2" t="s">
@@ -1465,883 +1485,861 @@
       <c r="K3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="L3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="M3" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="N3" s="58" t="s">
+      <c r="N3" s="96" t="s">
+        <v>74</v>
+      </c>
+      <c r="O3" s="68" t="s">
         <v>19</v>
       </c>
-      <c r="O3" s="103" t="s">
-        <v>75</v>
-      </c>
-      <c r="P3" s="75" t="s">
+      <c r="P3" s="68" t="s">
         <v>20</v>
       </c>
-      <c r="Q3" s="75" t="s">
+      <c r="Q3" s="68" t="s">
         <v>21</v>
       </c>
-      <c r="R3" s="75" t="s">
-        <v>22</v>
-      </c>
-      <c r="S3" s="58" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R3" s="51" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4">
         <v>1</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="D4" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E4" s="53" t="s">
-        <v>26</v>
-      </c>
-      <c r="F4" s="59">
+      <c r="E4" s="52">
         <v>22.103000000000002</v>
       </c>
-      <c r="G4" s="60">
+      <c r="F4" s="53">
         <v>24.64</v>
       </c>
-      <c r="H4" s="61">
+      <c r="G4" s="54">
         <v>26.946000000000002</v>
       </c>
-      <c r="I4" s="62">
+      <c r="H4" s="55">
         <v>23.960999999999999</v>
       </c>
-      <c r="J4" s="63">
+      <c r="I4" s="56">
         <v>26.754999999999999</v>
       </c>
-      <c r="K4" s="64">
+      <c r="J4" s="57">
         <v>24.667999999999999</v>
       </c>
-      <c r="L4" s="65">
+      <c r="K4" s="58">
         <v>27.027999999999999</v>
       </c>
-      <c r="M4" s="71">
+      <c r="L4" s="64">
         <v>84.994</v>
       </c>
-      <c r="N4" s="71">
-        <v>83.61</v>
-      </c>
-      <c r="O4" s="105">
-        <f>+(N4/M4)-1</f>
-        <v>-1.6283502364872859E-2</v>
-      </c>
-      <c r="P4" s="76">
+      <c r="M4" s="64">
+        <v>88.91</v>
+      </c>
+      <c r="N4" s="98">
+        <f>+(M4/L4)-1</f>
+        <v>4.6073840506388741E-2</v>
+      </c>
+      <c r="O4" s="69">
         <v>0.24099999999999999</v>
       </c>
-      <c r="Q4" s="76">
+      <c r="P4" s="69">
         <v>0.99299999999999999</v>
       </c>
-      <c r="R4" s="77">
+      <c r="Q4" s="70">
         <v>1.2330000000000001</v>
       </c>
-      <c r="S4" s="71"/>
-    </row>
-    <row r="5" spans="1:19" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R4" s="64"/>
+    </row>
+    <row r="5" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="9">
         <v>2</v>
       </c>
       <c r="B5" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="D5" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="E5" s="53" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" s="59">
+      <c r="E5" s="52">
         <v>-0.65300000000000002</v>
       </c>
-      <c r="G5" s="60">
+      <c r="F5" s="53">
         <v>-0.78400000000000003</v>
       </c>
-      <c r="H5" s="61">
+      <c r="G5" s="54">
         <v>-0.94</v>
       </c>
-      <c r="I5" s="62">
+      <c r="H5" s="55">
         <v>-1.1279999999999999</v>
       </c>
-      <c r="J5" s="63">
+      <c r="I5" s="56">
         <v>-1.3540000000000001</v>
       </c>
-      <c r="K5" s="64">
+      <c r="J5" s="57">
         <v>-1.625</v>
       </c>
-      <c r="L5" s="65">
+      <c r="K5" s="58">
         <v>-1.95</v>
       </c>
-      <c r="M5" s="71">
+      <c r="L5" s="64">
         <v>39.19</v>
       </c>
-      <c r="N5" s="71">
-        <v>33.667000000000002</v>
-      </c>
-      <c r="O5" s="105">
-        <f t="shared" ref="O5:O17" si="0">+(N5/M5)-1</f>
-        <v>-0.14092880836948196</v>
-      </c>
-      <c r="P5" s="78">
+      <c r="M5" s="64">
+        <v>36.840000000000003</v>
+      </c>
+      <c r="N5" s="98">
+        <f t="shared" ref="N5:N17" si="0">+(M5/L5)-1</f>
+        <v>-5.9964276601173649E-2</v>
+      </c>
+      <c r="O5" s="71">
         <v>0.122</v>
       </c>
-      <c r="Q5" s="78">
+      <c r="P5" s="71">
         <v>0.36699999999999999</v>
       </c>
-      <c r="R5" s="79">
+      <c r="Q5" s="72">
         <v>0.48899999999999999</v>
       </c>
-      <c r="S5" s="71"/>
-    </row>
-    <row r="6" spans="1:19" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R5" s="64"/>
+    </row>
+    <row r="6" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="13">
         <v>3</v>
       </c>
       <c r="B6" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="D6" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="E6" s="54" t="s">
-        <v>33</v>
-      </c>
-      <c r="F6" s="59">
+      <c r="E6" s="52">
         <v>2.34</v>
       </c>
-      <c r="G6" s="60">
+      <c r="F6" s="53">
         <v>2.48</v>
       </c>
-      <c r="H6" s="61">
+      <c r="G6" s="54">
         <v>2.65</v>
       </c>
-      <c r="I6" s="62">
+      <c r="H6" s="55">
         <v>2.4060000000000001</v>
       </c>
-      <c r="J6" s="63">
+      <c r="I6" s="56">
         <v>3.206</v>
       </c>
-      <c r="K6" s="64">
+      <c r="J6" s="57">
         <v>3.0350000000000001</v>
       </c>
-      <c r="L6" s="65">
+      <c r="K6" s="58">
         <v>3.0089999999999999</v>
       </c>
-      <c r="M6" s="71">
+      <c r="L6" s="64">
         <v>24.951000000000001</v>
       </c>
-      <c r="N6" s="71"/>
-      <c r="O6" s="105"/>
-      <c r="P6" s="80">
+      <c r="M6" s="64"/>
+      <c r="N6" s="98"/>
+      <c r="O6" s="73">
         <v>1.0780000000000001</v>
       </c>
-      <c r="Q6" s="80">
+      <c r="P6" s="73">
         <v>0.52800000000000002</v>
       </c>
-      <c r="R6" s="77">
+      <c r="Q6" s="70">
         <v>1.6060000000000001</v>
       </c>
-      <c r="S6" s="71"/>
-    </row>
-    <row r="7" spans="1:19" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R6" s="64"/>
+    </row>
+    <row r="7" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="13">
         <v>4</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C7" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="E7" s="55" t="s">
-        <v>35</v>
-      </c>
-      <c r="F7" s="59">
+      <c r="E7" s="52">
         <v>2.34</v>
       </c>
-      <c r="G7" s="60">
+      <c r="F7" s="53">
         <v>2.48</v>
       </c>
-      <c r="H7" s="61">
+      <c r="G7" s="54">
         <v>2.65</v>
       </c>
-      <c r="I7" s="62">
+      <c r="H7" s="55">
         <v>2.4060000000000001</v>
       </c>
-      <c r="J7" s="63">
+      <c r="I7" s="56">
         <v>3.206</v>
       </c>
-      <c r="K7" s="64">
+      <c r="J7" s="57">
         <v>3.0350000000000001</v>
       </c>
-      <c r="L7" s="65">
+      <c r="K7" s="58">
         <v>3.0089999999999999</v>
       </c>
-      <c r="M7" s="71">
+      <c r="L7" s="64">
         <v>9.5299999999999994</v>
       </c>
-      <c r="N7" s="71"/>
-      <c r="O7" s="105"/>
-      <c r="P7" s="80">
+      <c r="M7" s="64"/>
+      <c r="N7" s="98"/>
+      <c r="O7" s="73">
         <v>0.153</v>
       </c>
-      <c r="Q7" s="80">
+      <c r="P7" s="73">
         <v>0.46</v>
       </c>
-      <c r="R7" s="79">
+      <c r="Q7" s="72">
         <v>0.61299999999999999</v>
       </c>
-      <c r="S7" s="71"/>
-    </row>
-    <row r="8" spans="1:19" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R7" s="64"/>
+    </row>
+    <row r="8" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="18">
         <v>5</v>
       </c>
       <c r="B8" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="C8" s="20" t="s">
+      <c r="D8" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="D8" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="E8" s="53" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" s="59">
+      <c r="E8" s="52">
         <v>23.295999999999999</v>
       </c>
-      <c r="G8" s="60">
+      <c r="F8" s="53">
         <v>24.047999999999998</v>
       </c>
-      <c r="H8" s="61">
+      <c r="G8" s="54">
         <v>24.824999999999999</v>
       </c>
-      <c r="I8" s="62">
+      <c r="H8" s="55">
         <v>23.427</v>
       </c>
-      <c r="J8" s="63">
+      <c r="I8" s="56">
         <v>26.088999999999999</v>
       </c>
-      <c r="K8" s="64">
+      <c r="J8" s="57">
         <v>27.76</v>
       </c>
-      <c r="L8" s="65">
+      <c r="K8" s="58">
         <v>32.539000000000001</v>
       </c>
-      <c r="M8" s="71">
+      <c r="L8" s="64">
         <v>69.394999999999996</v>
       </c>
-      <c r="N8" s="71"/>
-      <c r="O8" s="105"/>
-      <c r="P8" s="81">
+      <c r="M8" s="64"/>
+      <c r="N8" s="98"/>
+      <c r="O8" s="74">
         <v>1.8680000000000001</v>
       </c>
-      <c r="Q8" s="81">
+      <c r="P8" s="74">
         <v>5.6040000000000001</v>
       </c>
-      <c r="R8" s="82">
+      <c r="Q8" s="75">
         <v>7.4720000000000004</v>
       </c>
-      <c r="S8" s="71"/>
-    </row>
-    <row r="9" spans="1:19" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R8" s="64"/>
+    </row>
+    <row r="9" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="18">
         <v>6</v>
       </c>
       <c r="B9" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" s="52">
+        <v>23.295999999999999</v>
+      </c>
+      <c r="F9" s="53">
+        <v>24.047999999999998</v>
+      </c>
+      <c r="G9" s="54">
+        <v>24.824999999999999</v>
+      </c>
+      <c r="H9" s="55">
+        <v>23.427</v>
+      </c>
+      <c r="I9" s="56">
+        <v>26.088999999999999</v>
+      </c>
+      <c r="J9" s="57">
+        <v>27.76</v>
+      </c>
+      <c r="K9" s="58">
+        <v>32.539000000000001</v>
+      </c>
+      <c r="L9" s="64">
+        <v>24.693000000000001</v>
+      </c>
+      <c r="M9" s="64"/>
+      <c r="N9" s="98"/>
+      <c r="O9" s="74">
+        <v>3.238</v>
+      </c>
+      <c r="P9" s="74">
+        <v>9.7149999999999999</v>
+      </c>
+      <c r="Q9" s="76">
+        <v>12.954000000000001</v>
+      </c>
+      <c r="R9" s="64"/>
+    </row>
+    <row r="10" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="99">
+        <v>7</v>
+      </c>
+      <c r="B10" s="100" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="E9" s="53" t="s">
-        <v>26</v>
-      </c>
-      <c r="F9" s="59">
-        <v>23.295999999999999</v>
-      </c>
-      <c r="G9" s="60">
-        <v>24.047999999999998</v>
-      </c>
-      <c r="H9" s="61">
-        <v>24.824999999999999</v>
-      </c>
-      <c r="I9" s="62">
-        <v>23.427</v>
-      </c>
-      <c r="J9" s="63">
-        <v>26.088999999999999</v>
-      </c>
-      <c r="K9" s="64">
-        <v>27.76</v>
-      </c>
-      <c r="L9" s="65">
-        <v>32.539000000000001</v>
-      </c>
-      <c r="M9" s="71">
-        <v>24.693000000000001</v>
-      </c>
-      <c r="N9" s="71"/>
-      <c r="O9" s="105"/>
-      <c r="P9" s="81">
-        <v>3.238</v>
-      </c>
-      <c r="Q9" s="81">
-        <v>9.7149999999999999</v>
-      </c>
-      <c r="R9" s="83">
-        <v>12.954000000000001</v>
-      </c>
-      <c r="S9" s="71"/>
-    </row>
-    <row r="10" spans="1:19" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="21">
-        <v>7</v>
-      </c>
-      <c r="B10" s="22" t="s">
+      <c r="C10" s="101" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="23" t="s">
+      <c r="D10" s="100" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="E10" s="56" t="s">
-        <v>43</v>
-      </c>
-      <c r="F10" s="59">
+      <c r="E10" s="52">
         <v>1.244</v>
       </c>
-      <c r="G10" s="60">
+      <c r="F10" s="53">
         <v>1.367</v>
       </c>
-      <c r="H10" s="61">
+      <c r="G10" s="54">
         <v>1.282</v>
       </c>
-      <c r="I10" s="62">
+      <c r="H10" s="55">
         <v>1.331</v>
       </c>
-      <c r="J10" s="63">
+      <c r="I10" s="56">
         <v>1.5249999999999999</v>
       </c>
-      <c r="K10" s="64">
+      <c r="J10" s="57">
         <v>1.698</v>
       </c>
-      <c r="L10" s="65">
+      <c r="K10" s="58">
         <v>1.51</v>
       </c>
-      <c r="M10" s="71">
+      <c r="L10" s="64">
         <v>1.135</v>
       </c>
-      <c r="N10" s="71"/>
-      <c r="O10" s="105"/>
-      <c r="P10" s="84">
+      <c r="M10" s="64">
+        <v>2.38</v>
+      </c>
+      <c r="N10" s="98">
+        <f t="shared" si="0"/>
+        <v>1.0969162995594712</v>
+      </c>
+      <c r="O10" s="77">
         <v>0</v>
       </c>
-      <c r="Q10" s="84">
+      <c r="P10" s="77">
         <v>0</v>
       </c>
-      <c r="R10" s="85">
+      <c r="Q10" s="78">
         <v>0</v>
       </c>
-      <c r="S10" s="71"/>
-    </row>
-    <row r="11" spans="1:19" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R10" s="64"/>
+    </row>
+    <row r="11" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="13">
         <v>8</v>
       </c>
       <c r="B11" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="D11" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="E11" s="52">
+        <v>1.5089999999999999</v>
+      </c>
+      <c r="F11" s="53">
+        <v>1.64</v>
+      </c>
+      <c r="G11" s="54">
+        <v>1.794</v>
+      </c>
+      <c r="H11" s="55">
+        <v>1.57</v>
+      </c>
+      <c r="I11" s="56">
+        <v>2.2730000000000001</v>
+      </c>
+      <c r="J11" s="57">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="K11" s="58">
+        <v>1.98</v>
+      </c>
+      <c r="L11" s="64">
+        <v>1.69</v>
+      </c>
+      <c r="M11" s="64">
+        <v>3.71</v>
+      </c>
+      <c r="N11" s="98">
+        <f t="shared" si="0"/>
+        <v>1.195266272189349</v>
+      </c>
+      <c r="O11" s="73">
+        <v>0.10100000000000001</v>
+      </c>
+      <c r="P11" s="73">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="Q11" s="72">
+        <v>0.109</v>
+      </c>
+      <c r="R11" s="64"/>
+    </row>
+    <row r="12" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="102">
+        <v>9</v>
+      </c>
+      <c r="B12" s="103" t="s">
         <v>45</v>
       </c>
-      <c r="D11" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="E11" s="56" t="s">
-        <v>43</v>
-      </c>
-      <c r="F11" s="59">
-        <v>1.5089999999999999</v>
-      </c>
-      <c r="G11" s="60">
-        <v>1.64</v>
-      </c>
-      <c r="H11" s="61">
-        <v>1.794</v>
-      </c>
-      <c r="I11" s="62">
-        <v>1.57</v>
-      </c>
-      <c r="J11" s="63">
-        <v>2.2730000000000001</v>
-      </c>
-      <c r="K11" s="64">
-        <v>2.0699999999999998</v>
-      </c>
-      <c r="L11" s="65">
-        <v>1.98</v>
-      </c>
-      <c r="M11" s="71">
-        <v>1.69</v>
-      </c>
-      <c r="N11" s="71"/>
-      <c r="O11" s="105"/>
-      <c r="P11" s="80">
-        <v>0.10100000000000001</v>
-      </c>
-      <c r="Q11" s="80">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="R11" s="79">
-        <v>0.109</v>
-      </c>
-      <c r="S11" s="71"/>
-    </row>
-    <row r="12" spans="1:19" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="25">
-        <v>9</v>
-      </c>
-      <c r="B12" s="26" t="s">
+      <c r="C12" s="104" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="27" t="s">
+      <c r="D12" s="103" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="26" t="s">
+      <c r="E12" s="52">
+        <v>2.3149999999999999</v>
+      </c>
+      <c r="F12" s="53">
+        <v>2.4510000000000001</v>
+      </c>
+      <c r="G12" s="54">
+        <v>2.9289999999999998</v>
+      </c>
+      <c r="H12" s="55">
+        <v>2.5819999999999999</v>
+      </c>
+      <c r="I12" s="56">
+        <v>3.4420000000000002</v>
+      </c>
+      <c r="J12" s="57">
+        <v>3.3959999999999999</v>
+      </c>
+      <c r="K12" s="58">
+        <v>4.0430000000000001</v>
+      </c>
+      <c r="L12" s="64">
+        <v>1.482</v>
+      </c>
+      <c r="M12" s="64">
+        <v>1.3080000000000001</v>
+      </c>
+      <c r="N12" s="98">
+        <f t="shared" si="0"/>
+        <v>-0.11740890688259109</v>
+      </c>
+      <c r="O12" s="79">
+        <v>6.2E-2</v>
+      </c>
+      <c r="P12" s="79">
+        <v>0.161</v>
+      </c>
+      <c r="Q12" s="72">
+        <v>0.224</v>
+      </c>
+      <c r="R12" s="64"/>
+    </row>
+    <row r="13" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="105">
+        <v>10</v>
+      </c>
+      <c r="B13" s="106" t="s">
         <v>48</v>
       </c>
-      <c r="E12" s="55" t="s">
-        <v>35</v>
-      </c>
-      <c r="F12" s="59">
-        <v>2.3149999999999999</v>
-      </c>
-      <c r="G12" s="60">
-        <v>2.4510000000000001</v>
-      </c>
-      <c r="H12" s="61">
-        <v>2.9289999999999998</v>
-      </c>
-      <c r="I12" s="62">
-        <v>2.5819999999999999</v>
-      </c>
-      <c r="J12" s="63">
-        <v>3.4420000000000002</v>
-      </c>
-      <c r="K12" s="64">
-        <v>3.3959999999999999</v>
-      </c>
-      <c r="L12" s="65">
-        <v>4.0430000000000001</v>
-      </c>
-      <c r="M12" s="71">
-        <v>1.482</v>
-      </c>
-      <c r="N12" s="71"/>
-      <c r="O12" s="105"/>
-      <c r="P12" s="86">
-        <v>6.2E-2</v>
-      </c>
-      <c r="Q12" s="86">
-        <v>0.161</v>
-      </c>
-      <c r="R12" s="79">
-        <v>0.224</v>
-      </c>
-      <c r="S12" s="71"/>
-    </row>
-    <row r="13" spans="1:19" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="28">
-        <v>10</v>
-      </c>
-      <c r="B13" s="29" t="s">
+      <c r="C13" s="107" t="s">
         <v>49</v>
       </c>
-      <c r="C13" s="30" t="s">
+      <c r="D13" s="106" t="s">
         <v>50</v>
       </c>
-      <c r="D13" s="29" t="s">
+      <c r="E13" s="52">
+        <v>3.609</v>
+      </c>
+      <c r="F13" s="53">
+        <v>3.343</v>
+      </c>
+      <c r="G13" s="54">
+        <v>3.706</v>
+      </c>
+      <c r="H13" s="55">
+        <v>3.367</v>
+      </c>
+      <c r="I13" s="56">
+        <v>4.0309999999999997</v>
+      </c>
+      <c r="J13" s="57">
+        <v>4.1760000000000002</v>
+      </c>
+      <c r="K13" s="58">
+        <v>4.8780000000000001</v>
+      </c>
+      <c r="L13" s="64">
+        <v>1.863</v>
+      </c>
+      <c r="M13" s="64">
+        <v>2.004</v>
+      </c>
+      <c r="N13" s="98">
+        <f t="shared" si="0"/>
+        <v>7.5684380032206233E-2</v>
+      </c>
+      <c r="O13" s="77">
+        <v>0</v>
+      </c>
+      <c r="P13" s="80">
+        <v>0.373</v>
+      </c>
+      <c r="Q13" s="72">
+        <v>0.373</v>
+      </c>
+      <c r="R13" s="64"/>
+    </row>
+    <row r="14" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="28">
+        <v>11</v>
+      </c>
+      <c r="B14" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="E13" s="55" t="s">
-        <v>35</v>
-      </c>
-      <c r="F13" s="59">
-        <v>3.609</v>
-      </c>
-      <c r="G13" s="60">
-        <v>3.343</v>
-      </c>
-      <c r="H13" s="61">
-        <v>3.706</v>
-      </c>
-      <c r="I13" s="62">
-        <v>3.367</v>
-      </c>
-      <c r="J13" s="63">
-        <v>4.0309999999999997</v>
-      </c>
-      <c r="K13" s="64">
-        <v>4.1760000000000002</v>
-      </c>
-      <c r="L13" s="65">
-        <v>4.8780000000000001</v>
-      </c>
-      <c r="M13" s="71">
-        <v>1.863</v>
-      </c>
-      <c r="N13" s="71"/>
-      <c r="O13" s="105"/>
-      <c r="P13" s="84">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="87">
-        <v>0.373</v>
-      </c>
-      <c r="R13" s="79">
-        <v>0.373</v>
-      </c>
-      <c r="S13" s="71"/>
-    </row>
-    <row r="14" spans="1:19" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="31">
-        <v>11</v>
-      </c>
-      <c r="B14" s="32" t="s">
+      <c r="C14" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="C14" s="33" t="s">
+      <c r="D14" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="D14" s="32" t="s">
-        <v>54</v>
-      </c>
-      <c r="E14" s="55" t="s">
-        <v>35</v>
-      </c>
-      <c r="F14" s="59">
+      <c r="E14" s="52">
         <v>0.54900000000000004</v>
       </c>
-      <c r="G14" s="60">
+      <c r="F14" s="53">
         <v>0.58699999999999997</v>
       </c>
-      <c r="H14" s="61">
+      <c r="G14" s="54">
         <v>0.624</v>
       </c>
-      <c r="I14" s="62">
+      <c r="H14" s="55">
         <v>0.66</v>
       </c>
-      <c r="J14" s="63">
+      <c r="I14" s="56">
         <v>0.69499999999999995</v>
       </c>
-      <c r="K14" s="64">
+      <c r="J14" s="57">
         <v>0.72899999999999998</v>
       </c>
-      <c r="L14" s="65">
+      <c r="K14" s="58">
         <v>0.76200000000000001</v>
       </c>
-      <c r="M14" s="71">
+      <c r="L14" s="64">
         <v>1.5429999999999999</v>
       </c>
-      <c r="N14" s="71">
+      <c r="M14" s="64">
         <v>1.65</v>
       </c>
-      <c r="O14" s="105">
+      <c r="N14" s="98">
         <f t="shared" si="0"/>
         <v>6.934543097861301E-2</v>
       </c>
-      <c r="P14" s="88">
+      <c r="O14" s="81">
         <v>7.0999999999999994E-2</v>
       </c>
-      <c r="Q14" s="88">
+      <c r="P14" s="81">
         <v>0.108</v>
       </c>
-      <c r="R14" s="79">
+      <c r="Q14" s="72">
         <v>0.17899999999999999</v>
       </c>
-      <c r="S14" s="71"/>
-    </row>
-    <row r="15" spans="1:19" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="31">
+      <c r="R14" s="64"/>
+    </row>
+    <row r="15" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="28">
         <v>12</v>
       </c>
-      <c r="B15" s="32" t="s">
+      <c r="B15" s="29" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="C15" s="33" t="s">
-        <v>56</v>
-      </c>
-      <c r="D15" s="32" t="s">
-        <v>54</v>
-      </c>
-      <c r="E15" s="56" t="s">
-        <v>43</v>
-      </c>
-      <c r="F15" s="59">
+      <c r="D15" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="E15" s="52">
         <v>0.496</v>
       </c>
-      <c r="G15" s="60">
+      <c r="F15" s="53">
         <v>0.503</v>
       </c>
-      <c r="H15" s="61">
+      <c r="G15" s="54">
         <v>0.47699999999999998</v>
       </c>
-      <c r="I15" s="62">
+      <c r="H15" s="55">
         <v>0.48199999999999998</v>
       </c>
-      <c r="J15" s="63">
+      <c r="I15" s="56">
         <v>0.48699999999999999</v>
       </c>
-      <c r="K15" s="64">
+      <c r="J15" s="57">
         <v>0.49199999999999999</v>
       </c>
-      <c r="L15" s="65">
+      <c r="K15" s="58">
         <v>0.496</v>
       </c>
-      <c r="M15" s="71">
+      <c r="L15" s="64">
         <v>0.25800000000000001</v>
       </c>
-      <c r="N15" s="71">
+      <c r="M15" s="64">
         <v>0.25319999999999998</v>
       </c>
-      <c r="O15" s="105">
+      <c r="N15" s="98">
         <f t="shared" si="0"/>
         <v>-1.8604651162790753E-2</v>
       </c>
-      <c r="P15" s="88">
+      <c r="O15" s="81">
         <v>2.4E-2</v>
       </c>
-      <c r="Q15" s="88">
+      <c r="P15" s="81">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="R15" s="79">
+      <c r="Q15" s="72">
         <v>0.06</v>
       </c>
-      <c r="S15" s="71"/>
-    </row>
-    <row r="16" spans="1:19" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="35">
+      <c r="R15" s="64"/>
+    </row>
+    <row r="16" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="32">
         <v>13</v>
       </c>
-      <c r="B16" s="36" t="s">
+      <c r="B16" s="33" t="s">
+        <v>56</v>
+      </c>
+      <c r="C16" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="C16" s="37" t="s">
+      <c r="D16" s="33" t="s">
         <v>58</v>
       </c>
-      <c r="D16" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="E16" s="55" t="s">
-        <v>35</v>
-      </c>
-      <c r="F16" s="59">
+      <c r="E16" s="52">
         <v>3.298</v>
       </c>
-      <c r="G16" s="60">
+      <c r="F16" s="53">
         <v>3.5670000000000002</v>
       </c>
-      <c r="H16" s="61">
+      <c r="G16" s="54">
         <v>3.39</v>
       </c>
-      <c r="I16" s="62">
+      <c r="H16" s="55">
         <v>3.375</v>
       </c>
-      <c r="J16" s="63">
+      <c r="I16" s="56">
         <v>3.3610000000000002</v>
       </c>
-      <c r="K16" s="64">
+      <c r="J16" s="57">
         <v>3.403</v>
       </c>
-      <c r="L16" s="65">
+      <c r="K16" s="58">
         <v>3.4289999999999998</v>
       </c>
-      <c r="M16" s="74">
+      <c r="L16" s="67">
         <v>3.919</v>
       </c>
-      <c r="N16" s="71">
+      <c r="M16" s="64">
         <v>4.1029999999999998</v>
       </c>
-      <c r="O16" s="105">
+      <c r="N16" s="98">
         <f t="shared" si="0"/>
         <v>4.6950752743046609E-2</v>
       </c>
-      <c r="P16" s="89">
+      <c r="O16" s="82">
         <v>1.2E-2</v>
       </c>
-      <c r="Q16" s="89">
+      <c r="P16" s="82">
         <v>3.6999999999999998E-2</v>
       </c>
-      <c r="R16" s="79">
+      <c r="Q16" s="72">
         <v>4.9000000000000002E-2</v>
       </c>
-      <c r="S16" s="71"/>
-    </row>
-    <row r="17" spans="1:19" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="38">
+      <c r="R16" s="64"/>
+    </row>
+    <row r="17" spans="1:18" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="35">
         <v>14</v>
       </c>
-      <c r="B17" s="39" t="s">
+      <c r="B17" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="C17" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="C17" s="40" t="s">
+      <c r="D17" s="36" t="s">
         <v>61</v>
       </c>
-      <c r="D17" s="39" t="s">
-        <v>62</v>
-      </c>
-      <c r="E17" s="54" t="s">
-        <v>33</v>
-      </c>
-      <c r="F17" s="59">
+      <c r="E17" s="52">
         <v>19.795000000000002</v>
       </c>
-      <c r="G17" s="60">
+      <c r="F17" s="53">
         <v>19.149000000000001</v>
       </c>
-      <c r="H17" s="61">
+      <c r="G17" s="54">
         <v>20.071999999999999</v>
       </c>
-      <c r="I17" s="62">
+      <c r="H17" s="55">
         <v>19.292999999999999</v>
       </c>
-      <c r="J17" s="63">
+      <c r="I17" s="56">
         <v>22.452999999999999</v>
       </c>
-      <c r="K17" s="64">
+      <c r="J17" s="57">
         <v>25.193000000000001</v>
       </c>
-      <c r="L17" s="65">
+      <c r="K17" s="58">
         <v>23.402999999999999</v>
       </c>
-      <c r="M17" s="71">
+      <c r="L17" s="64">
         <v>12.920999999999999</v>
       </c>
-      <c r="N17" s="71">
+      <c r="M17" s="64">
         <v>12.85</v>
       </c>
-      <c r="O17" s="105">
+      <c r="N17" s="98">
         <f t="shared" si="0"/>
         <v>-5.494930732915404E-3</v>
       </c>
-      <c r="P17" s="90">
+      <c r="O17" s="83">
         <v>2.4159999999999999</v>
       </c>
-      <c r="Q17" s="90">
+      <c r="P17" s="83">
         <v>3.2829999999999999</v>
       </c>
-      <c r="R17" s="82">
+      <c r="Q17" s="75">
         <v>5.6989999999999998</v>
       </c>
-      <c r="S17" s="71"/>
-    </row>
-    <row r="18" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="41" t="s">
+      <c r="R17" s="64"/>
+    </row>
+    <row r="18" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="38" t="s">
+        <v>62</v>
+      </c>
+      <c r="B18" s="38" t="s">
         <v>63</v>
       </c>
-      <c r="B18" s="41" t="s">
+      <c r="C18" s="38"/>
+      <c r="D18" s="38"/>
+      <c r="E18" s="62">
+        <v>76.076999999999998</v>
+      </c>
+      <c r="F18" s="62">
+        <v>78.900000000000006</v>
+      </c>
+      <c r="G18" s="62">
+        <v>83.031999999999996</v>
+      </c>
+      <c r="H18" s="62">
+        <v>77.174000000000007</v>
+      </c>
+      <c r="I18" s="62">
+        <v>87.248000000000005</v>
+      </c>
+      <c r="J18" s="62">
+        <v>89.528999999999996</v>
+      </c>
+      <c r="K18" s="63">
+        <v>95.103999999999999</v>
+      </c>
+      <c r="L18" s="65">
+        <f>+SUM(L4:L17)</f>
+        <v>277.56399999999996</v>
+      </c>
+      <c r="M18" s="66">
+        <f>+SUM(M4:M17)</f>
+        <v>154.00819999999999</v>
+      </c>
+      <c r="N18" s="97"/>
+      <c r="O18" s="84">
+        <v>9.3859999999999992</v>
+      </c>
+      <c r="P18" s="84">
+        <v>21.672000000000001</v>
+      </c>
+      <c r="Q18" s="84">
+        <v>31.06</v>
+      </c>
+      <c r="R18" s="66">
+        <f>+SUM(R4:R17)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="90" t="s">
         <v>64</v>
       </c>
-      <c r="C18" s="41"/>
-      <c r="D18" s="41"/>
-      <c r="E18" s="41"/>
-      <c r="F18" s="69">
-        <v>76.076999999999998</v>
-      </c>
-      <c r="G18" s="69">
-        <v>78.900000000000006</v>
-      </c>
-      <c r="H18" s="69">
-        <v>83.031999999999996</v>
-      </c>
-      <c r="I18" s="69">
-        <v>77.174000000000007</v>
-      </c>
-      <c r="J18" s="69">
-        <v>87.248000000000005</v>
-      </c>
-      <c r="K18" s="69">
-        <v>89.528999999999996</v>
-      </c>
-      <c r="L18" s="70">
-        <v>95.103999999999999</v>
-      </c>
-      <c r="M18" s="72">
-        <f>+SUM(M4:M17)</f>
-        <v>277.56399999999996</v>
-      </c>
-      <c r="N18" s="73">
-        <f>+SUM(N4:N17)</f>
-        <v>136.13320000000002</v>
-      </c>
-      <c r="O18" s="104"/>
-      <c r="P18" s="91">
-        <v>9.3859999999999992</v>
-      </c>
-      <c r="Q18" s="91">
-        <v>21.672000000000001</v>
-      </c>
-      <c r="R18" s="91">
-        <v>31.06</v>
-      </c>
-      <c r="S18" s="73">
-        <f>+SUM(S4:S17)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="97" t="s">
-        <v>65</v>
-      </c>
-      <c r="B20" s="93"/>
-      <c r="C20" s="93"/>
-      <c r="D20" s="93"/>
-      <c r="E20" s="93"/>
-      <c r="F20" s="93"/>
-      <c r="G20" s="93"/>
-      <c r="H20" s="93"/>
-      <c r="I20" s="93"/>
-      <c r="J20" s="93"/>
-      <c r="K20" s="93"/>
-      <c r="L20" s="93"/>
-      <c r="M20" s="93"/>
-      <c r="N20" s="93"/>
+      <c r="B20" s="86"/>
+      <c r="C20" s="86"/>
+      <c r="D20" s="86"/>
+      <c r="E20" s="86"/>
+      <c r="F20" s="86"/>
+      <c r="G20" s="86"/>
+      <c r="H20" s="86"/>
+      <c r="I20" s="86"/>
+      <c r="J20" s="86"/>
+      <c r="K20" s="86"/>
+      <c r="L20" s="86"/>
+      <c r="M20" s="86"/>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="C25" t="s">
+        <v>75</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A1:S1"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A20:N20"/>
-    <mergeCell ref="F2:L2"/>
-    <mergeCell ref="M2"/>
-    <mergeCell ref="P2:S2"/>
+    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A20:M20"/>
+    <mergeCell ref="E2:K2"/>
+    <mergeCell ref="L2"/>
+    <mergeCell ref="O2:R2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2363,43 +2361,43 @@
   <sheetData>
     <row r="1" spans="1:13" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -2407,40 +2405,40 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D2" s="59">
+        <v>25</v>
+      </c>
+      <c r="D2" s="52">
         <v>22.103000000000002</v>
       </c>
-      <c r="E2" s="60">
+      <c r="E2" s="53">
         <v>24.64</v>
       </c>
-      <c r="F2" s="61">
+      <c r="F2" s="54">
         <v>26.946000000000002</v>
       </c>
-      <c r="G2" s="62">
+      <c r="G2" s="55">
         <v>23.960999999999999</v>
       </c>
-      <c r="H2" s="63">
+      <c r="H2" s="56">
         <v>26.754999999999999</v>
       </c>
-      <c r="I2" s="64">
+      <c r="I2" s="57">
         <v>24.667999999999999</v>
       </c>
-      <c r="J2" s="65">
+      <c r="J2" s="58">
         <v>27.027999999999999</v>
       </c>
-      <c r="K2" s="67">
+      <c r="K2" s="60">
         <v>4.9249999999999998</v>
       </c>
       <c r="L2" s="8">
         <v>0.22282043161561779</v>
       </c>
-      <c r="M2" s="42" t="s">
-        <v>71</v>
+      <c r="M2" s="39" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -2448,40 +2446,40 @@
         <v>2</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" s="59">
+        <v>25</v>
+      </c>
+      <c r="D3" s="52">
         <v>-0.65300000000000002</v>
       </c>
-      <c r="E3" s="60">
+      <c r="E3" s="53">
         <v>-0.78400000000000003</v>
       </c>
-      <c r="F3" s="61">
+      <c r="F3" s="54">
         <v>-0.94</v>
       </c>
-      <c r="G3" s="62">
+      <c r="G3" s="55">
         <v>-1.1279999999999999</v>
       </c>
-      <c r="H3" s="63">
+      <c r="H3" s="56">
         <v>-1.3540000000000001</v>
       </c>
-      <c r="I3" s="64">
+      <c r="I3" s="57">
         <v>-1.625</v>
       </c>
-      <c r="J3" s="65">
+      <c r="J3" s="58">
         <v>-1.95</v>
       </c>
-      <c r="K3" s="66">
+      <c r="K3" s="59">
         <v>-1.2969999999999999</v>
       </c>
       <c r="L3" s="12">
         <v>-1.9862174578866769</v>
       </c>
-      <c r="M3" s="43" t="s">
-        <v>72</v>
+      <c r="M3" s="40" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -2489,40 +2487,40 @@
         <v>3</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" s="59">
+        <v>32</v>
+      </c>
+      <c r="D4" s="52">
         <v>2.34</v>
       </c>
-      <c r="E4" s="60">
+      <c r="E4" s="53">
         <v>2.48</v>
       </c>
-      <c r="F4" s="61">
+      <c r="F4" s="54">
         <v>2.65</v>
       </c>
-      <c r="G4" s="62">
+      <c r="G4" s="55">
         <v>2.4060000000000001</v>
       </c>
-      <c r="H4" s="63">
+      <c r="H4" s="56">
         <v>3.206</v>
       </c>
-      <c r="I4" s="64">
+      <c r="I4" s="57">
         <v>3.0350000000000001</v>
       </c>
-      <c r="J4" s="65">
+      <c r="J4" s="58">
         <v>3.0089999999999999</v>
       </c>
-      <c r="K4" s="67">
+      <c r="K4" s="60">
         <v>0.66900000000000004</v>
       </c>
       <c r="L4" s="8">
         <v>0.28589743589743588</v>
       </c>
-      <c r="M4" s="44" t="s">
-        <v>71</v>
+      <c r="M4" s="41" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -2530,40 +2528,40 @@
         <v>4</v>
       </c>
       <c r="B5" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="C5" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="D5" s="59">
+      <c r="D5" s="52">
         <v>2.34</v>
       </c>
-      <c r="E5" s="60">
+      <c r="E5" s="53">
         <v>2.48</v>
       </c>
-      <c r="F5" s="61">
+      <c r="F5" s="54">
         <v>2.65</v>
       </c>
-      <c r="G5" s="62">
+      <c r="G5" s="55">
         <v>2.4060000000000001</v>
       </c>
-      <c r="H5" s="63">
+      <c r="H5" s="56">
         <v>3.206</v>
       </c>
-      <c r="I5" s="64">
+      <c r="I5" s="57">
         <v>3.0350000000000001</v>
       </c>
-      <c r="J5" s="65">
+      <c r="J5" s="58">
         <v>3.0089999999999999</v>
       </c>
-      <c r="K5" s="67">
+      <c r="K5" s="60">
         <v>0.66900000000000004</v>
       </c>
       <c r="L5" s="8">
         <v>0.28589743589743588</v>
       </c>
-      <c r="M5" s="44" t="s">
-        <v>71</v>
+      <c r="M5" s="41" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -2571,40 +2569,40 @@
         <v>5</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" s="59">
+        <v>25</v>
+      </c>
+      <c r="D6" s="52">
         <v>23.295999999999999</v>
       </c>
-      <c r="E6" s="60">
+      <c r="E6" s="53">
         <v>24.047999999999998</v>
       </c>
-      <c r="F6" s="61">
+      <c r="F6" s="54">
         <v>24.824999999999999</v>
       </c>
-      <c r="G6" s="62">
+      <c r="G6" s="55">
         <v>23.427</v>
       </c>
-      <c r="H6" s="63">
+      <c r="H6" s="56">
         <v>26.088999999999999</v>
       </c>
-      <c r="I6" s="64">
+      <c r="I6" s="57">
         <v>27.76</v>
       </c>
-      <c r="J6" s="65">
+      <c r="J6" s="58">
         <v>32.539000000000001</v>
       </c>
-      <c r="K6" s="67">
+      <c r="K6" s="60">
         <v>9.2430000000000003</v>
       </c>
       <c r="L6" s="8">
         <v>0.39676339285714279</v>
       </c>
-      <c r="M6" s="45" t="s">
-        <v>71</v>
+      <c r="M6" s="42" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -2612,40 +2610,40 @@
         <v>6</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" s="59">
+        <v>25</v>
+      </c>
+      <c r="D7" s="52">
         <v>23.295999999999999</v>
       </c>
-      <c r="E7" s="60">
+      <c r="E7" s="53">
         <v>24.047999999999998</v>
       </c>
-      <c r="F7" s="61">
+      <c r="F7" s="54">
         <v>24.824999999999999</v>
       </c>
-      <c r="G7" s="62">
+      <c r="G7" s="55">
         <v>23.427</v>
       </c>
-      <c r="H7" s="63">
+      <c r="H7" s="56">
         <v>26.088999999999999</v>
       </c>
-      <c r="I7" s="64">
+      <c r="I7" s="57">
         <v>27.76</v>
       </c>
-      <c r="J7" s="65">
+      <c r="J7" s="58">
         <v>32.539000000000001</v>
       </c>
-      <c r="K7" s="67">
+      <c r="K7" s="60">
         <v>9.2430000000000003</v>
       </c>
       <c r="L7" s="8">
         <v>0.39676339285714279</v>
       </c>
-      <c r="M7" s="45" t="s">
-        <v>71</v>
+      <c r="M7" s="42" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -2653,40 +2651,40 @@
         <v>7</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="C8" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="D8" s="59">
+        <v>39</v>
+      </c>
+      <c r="C8" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" s="52">
         <v>1.244</v>
       </c>
-      <c r="E8" s="60">
+      <c r="E8" s="53">
         <v>1.367</v>
       </c>
-      <c r="F8" s="61">
+      <c r="F8" s="54">
         <v>1.282</v>
       </c>
-      <c r="G8" s="62">
+      <c r="G8" s="55">
         <v>1.331</v>
       </c>
-      <c r="H8" s="63">
+      <c r="H8" s="56">
         <v>1.5249999999999999</v>
       </c>
-      <c r="I8" s="64">
+      <c r="I8" s="57">
         <v>1.698</v>
       </c>
-      <c r="J8" s="65">
+      <c r="J8" s="58">
         <v>1.51</v>
       </c>
-      <c r="K8" s="67">
+      <c r="K8" s="60">
         <v>0.26600000000000001</v>
       </c>
       <c r="L8" s="8">
         <v>0.2138263665594855</v>
       </c>
-      <c r="M8" s="46" t="s">
-        <v>71</v>
+      <c r="M8" s="43" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -2694,286 +2692,286 @@
         <v>8</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="C9" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="D9" s="59">
+      <c r="C9" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" s="52">
         <v>1.5089999999999999</v>
       </c>
-      <c r="E9" s="60">
+      <c r="E9" s="53">
         <v>1.64</v>
       </c>
-      <c r="F9" s="61">
+      <c r="F9" s="54">
         <v>1.794</v>
       </c>
-      <c r="G9" s="62">
+      <c r="G9" s="55">
         <v>1.57</v>
       </c>
-      <c r="H9" s="63">
+      <c r="H9" s="56">
         <v>2.2730000000000001</v>
       </c>
-      <c r="I9" s="64">
+      <c r="I9" s="57">
         <v>2.0699999999999998</v>
       </c>
-      <c r="J9" s="65">
+      <c r="J9" s="58">
         <v>1.98</v>
       </c>
-      <c r="K9" s="67">
+      <c r="K9" s="60">
         <v>0.47099999999999997</v>
       </c>
       <c r="L9" s="8">
         <v>0.31212723658051689</v>
       </c>
-      <c r="M9" s="44" t="s">
-        <v>71</v>
+      <c r="M9" s="41" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="25">
+      <c r="A10" s="24">
         <v>9</v>
       </c>
-      <c r="B10" s="26" t="s">
-        <v>46</v>
+      <c r="B10" s="25" t="s">
+        <v>45</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" s="59">
+        <v>34</v>
+      </c>
+      <c r="D10" s="52">
         <v>2.3149999999999999</v>
       </c>
-      <c r="E10" s="60">
+      <c r="E10" s="53">
         <v>2.4510000000000001</v>
       </c>
-      <c r="F10" s="61">
+      <c r="F10" s="54">
         <v>2.9289999999999998</v>
       </c>
-      <c r="G10" s="62">
+      <c r="G10" s="55">
         <v>2.5819999999999999</v>
       </c>
-      <c r="H10" s="63">
+      <c r="H10" s="56">
         <v>3.4420000000000002</v>
       </c>
-      <c r="I10" s="64">
+      <c r="I10" s="57">
         <v>3.3959999999999999</v>
       </c>
-      <c r="J10" s="65">
+      <c r="J10" s="58">
         <v>4.0430000000000001</v>
       </c>
-      <c r="K10" s="67">
+      <c r="K10" s="60">
         <v>1.728</v>
       </c>
       <c r="L10" s="8">
         <v>0.74643628509719218</v>
       </c>
-      <c r="M10" s="47" t="s">
-        <v>71</v>
+      <c r="M10" s="44" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="28">
+      <c r="A11" s="26">
         <v>10</v>
       </c>
-      <c r="B11" s="29" t="s">
-        <v>49</v>
+      <c r="B11" s="27" t="s">
+        <v>48</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="D11" s="59">
+        <v>34</v>
+      </c>
+      <c r="D11" s="52">
         <v>3.609</v>
       </c>
-      <c r="E11" s="60">
+      <c r="E11" s="53">
         <v>3.343</v>
       </c>
-      <c r="F11" s="61">
+      <c r="F11" s="54">
         <v>3.706</v>
       </c>
-      <c r="G11" s="62">
+      <c r="G11" s="55">
         <v>3.367</v>
       </c>
-      <c r="H11" s="63">
+      <c r="H11" s="56">
         <v>4.0309999999999997</v>
       </c>
-      <c r="I11" s="64">
+      <c r="I11" s="57">
         <v>4.1760000000000002</v>
       </c>
-      <c r="J11" s="65">
+      <c r="J11" s="58">
         <v>4.8780000000000001</v>
       </c>
-      <c r="K11" s="67">
+      <c r="K11" s="60">
         <v>1.2689999999999999</v>
       </c>
       <c r="L11" s="8">
         <v>0.35162094763092272</v>
       </c>
-      <c r="M11" s="48" t="s">
-        <v>71</v>
+      <c r="M11" s="45" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="31">
+      <c r="A12" s="28">
         <v>11</v>
       </c>
-      <c r="B12" s="32" t="s">
-        <v>52</v>
+      <c r="B12" s="29" t="s">
+        <v>51</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="D12" s="59">
+        <v>34</v>
+      </c>
+      <c r="D12" s="52">
         <v>0.54900000000000004</v>
       </c>
-      <c r="E12" s="60">
+      <c r="E12" s="53">
         <v>0.58699999999999997</v>
       </c>
-      <c r="F12" s="61">
+      <c r="F12" s="54">
         <v>0.624</v>
       </c>
-      <c r="G12" s="62">
+      <c r="G12" s="55">
         <v>0.66</v>
       </c>
-      <c r="H12" s="63">
+      <c r="H12" s="56">
         <v>0.69499999999999995</v>
       </c>
-      <c r="I12" s="64">
+      <c r="I12" s="57">
         <v>0.72899999999999998</v>
       </c>
-      <c r="J12" s="65">
+      <c r="J12" s="58">
         <v>0.76200000000000001</v>
       </c>
-      <c r="K12" s="67">
+      <c r="K12" s="60">
         <v>0.21299999999999999</v>
       </c>
       <c r="L12" s="8">
         <v>0.38797814207650272</v>
       </c>
-      <c r="M12" s="49" t="s">
-        <v>71</v>
+      <c r="M12" s="46" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="31">
+      <c r="A13" s="28">
         <v>12</v>
       </c>
-      <c r="B13" s="32" t="s">
-        <v>55</v>
-      </c>
-      <c r="C13" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="D13" s="59">
+      <c r="B13" s="29" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" s="52">
         <v>0.496</v>
       </c>
-      <c r="E13" s="60">
+      <c r="E13" s="53">
         <v>0.503</v>
       </c>
-      <c r="F13" s="61">
+      <c r="F13" s="54">
         <v>0.47699999999999998</v>
       </c>
-      <c r="G13" s="62">
+      <c r="G13" s="55">
         <v>0.48199999999999998</v>
       </c>
-      <c r="H13" s="63">
+      <c r="H13" s="56">
         <v>0.48699999999999999</v>
       </c>
-      <c r="I13" s="64">
+      <c r="I13" s="57">
         <v>0.49199999999999999</v>
       </c>
-      <c r="J13" s="65">
+      <c r="J13" s="58">
         <v>0.496</v>
       </c>
-      <c r="K13" s="68">
+      <c r="K13" s="61">
         <v>0</v>
       </c>
-      <c r="L13" s="34">
+      <c r="L13" s="31">
         <v>0</v>
       </c>
-      <c r="M13" s="50" t="s">
-        <v>73</v>
+      <c r="M13" s="47" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="35">
+      <c r="A14" s="32">
         <v>13</v>
       </c>
-      <c r="B14" s="36" t="s">
-        <v>57</v>
+      <c r="B14" s="33" t="s">
+        <v>56</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="D14" s="59">
+        <v>34</v>
+      </c>
+      <c r="D14" s="52">
         <v>3.298</v>
       </c>
-      <c r="E14" s="60">
+      <c r="E14" s="53">
         <v>3.5670000000000002</v>
       </c>
-      <c r="F14" s="61">
+      <c r="F14" s="54">
         <v>3.39</v>
       </c>
-      <c r="G14" s="62">
+      <c r="G14" s="55">
         <v>3.375</v>
       </c>
-      <c r="H14" s="63">
+      <c r="H14" s="56">
         <v>3.3610000000000002</v>
       </c>
-      <c r="I14" s="64">
+      <c r="I14" s="57">
         <v>3.403</v>
       </c>
-      <c r="J14" s="65">
+      <c r="J14" s="58">
         <v>3.4289999999999998</v>
       </c>
-      <c r="K14" s="67">
+      <c r="K14" s="60">
         <v>0.13100000000000001</v>
       </c>
       <c r="L14" s="8">
         <v>3.9721043056397808E-2</v>
       </c>
-      <c r="M14" s="51" t="s">
-        <v>71</v>
+      <c r="M14" s="48" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="38">
+      <c r="A15" s="35">
         <v>14</v>
       </c>
-      <c r="B15" s="39" t="s">
-        <v>60</v>
+      <c r="B15" s="36" t="s">
+        <v>59</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="D15" s="59">
+        <v>32</v>
+      </c>
+      <c r="D15" s="52">
         <v>19.795000000000002</v>
       </c>
-      <c r="E15" s="60">
+      <c r="E15" s="53">
         <v>19.149000000000001</v>
       </c>
-      <c r="F15" s="61">
+      <c r="F15" s="54">
         <v>20.071999999999999</v>
       </c>
-      <c r="G15" s="62">
+      <c r="G15" s="55">
         <v>19.292999999999999</v>
       </c>
-      <c r="H15" s="63">
+      <c r="H15" s="56">
         <v>22.452999999999999</v>
       </c>
-      <c r="I15" s="64">
+      <c r="I15" s="57">
         <v>25.193000000000001</v>
       </c>
-      <c r="J15" s="65">
+      <c r="J15" s="58">
         <v>23.402999999999999</v>
       </c>
-      <c r="K15" s="67">
+      <c r="K15" s="60">
         <v>3.6080000000000001</v>
       </c>
       <c r="L15" s="8">
         <v>0.18226824955796919</v>
       </c>
-      <c r="M15" s="52" t="s">
-        <v>71</v>
+      <c r="M15" s="49" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
